--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
+          <t>Thorleif Joelson, Henry Åkerström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29664-2025 artfynd.xlsx
+++ b/artfynd/A 29664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832294</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
